--- a/DEVELOPMENT_ALL_OLD_NEW/TOMMY-DEVELOPMENT PROTO AND SMS SAMPLER/TM.000600- SMS & PROTO TOMMY  BKA010 LIGHT BLUE RIGID -.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/TOMMY-DEVELOPMENT PROTO AND SMS SAMPLER/TM.000600- SMS & PROTO TOMMY  BKA010 LIGHT BLUE RIGID -.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25324E95-DCDF-40A6-A0B0-0E2B1AF2345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMS" sheetId="29" r:id="rId1"/>
@@ -1885,134 +1885,135 @@
     <xf numFmtId="164" fontId="16" fillId="5" borderId="59" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="4" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="33" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="52" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="55" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="48" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="50" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="46" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="47" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="24" fillId="4" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2042,135 +2043,134 @@
     <xf numFmtId="164" fontId="24" fillId="4" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="47" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="48" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="50" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="4" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="46" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="51" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="52" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="55" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="33" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="55" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="56" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="57" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="55" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -3267,21 +3267,21 @@
       <c r="B2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="225">
+      <c r="C2" s="152">
         <v>46274</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="228" t="s">
+      <c r="D2" s="153"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="G2" s="156"/>
+      <c r="H2" s="157" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="231"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="158"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
@@ -3290,19 +3290,19 @@
       <c r="B3" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="233"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="153"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="210"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="166"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
@@ -3311,17 +3311,17 @@
       <c r="B4" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="210"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="170"/>
+      <c r="K4" s="166"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
@@ -3330,17 +3330,17 @@
       <c r="B5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="222">
+      <c r="C5" s="167">
         <v>5160490</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="210"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="166"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="166"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
@@ -3349,17 +3349,17 @@
       <c r="B6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="222" t="s">
+      <c r="C6" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="223"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="234"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="209"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="209"/>
-      <c r="K6" s="210"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="166"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="166"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
@@ -3368,17 +3368,17 @@
       <c r="B7" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="223"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="209"/>
-      <c r="K7" s="210"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="166"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="166"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
@@ -3387,17 +3387,17 @@
       <c r="B8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="225" t="s">
+      <c r="C8" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="226"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="210"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="210"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="161"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="166"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
@@ -3406,15 +3406,15 @@
       <c r="B9" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="216"/>
-      <c r="D9" s="217"/>
-      <c r="E9" s="218"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="210"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="166"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
@@ -3423,15 +3423,15 @@
       <c r="B10" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="219"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="221"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="209"/>
-      <c r="I10" s="210"/>
-      <c r="J10" s="209"/>
-      <c r="K10" s="210"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="161"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="166"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -3440,13 +3440,13 @@
       <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="206"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="209"/>
-      <c r="I11" s="210"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="166"/>
       <c r="J11" s="53"/>
       <c r="K11" s="54"/>
       <c r="L11" s="2"/>
@@ -3457,15 +3457,15 @@
       <c r="B12" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="211"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="234"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="209"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="214"/>
-      <c r="K12" s="215"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="172"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
@@ -3474,13 +3474,13 @@
       <c r="B13" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="206"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="209"/>
-      <c r="I13" s="210"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="161"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="166"/>
       <c r="J13" s="35"/>
       <c r="K13" s="17"/>
       <c r="L13" s="2"/>
@@ -3491,17 +3491,17 @@
       <c r="B14" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="195" t="s">
+      <c r="C14" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="196"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="198" t="s">
+      <c r="D14" s="189"/>
+      <c r="E14" s="190"/>
+      <c r="F14" s="191" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="198"/>
-      <c r="H14" s="198"/>
-      <c r="I14" s="198"/>
+      <c r="G14" s="191"/>
+      <c r="H14" s="191"/>
+      <c r="I14" s="191"/>
       <c r="J14" s="36"/>
       <c r="K14" s="19"/>
       <c r="L14" s="2"/>
@@ -3519,11 +3519,11 @@
       <c r="E15" s="38">
         <v>1</v>
       </c>
-      <c r="F15" s="198"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="198"/>
-      <c r="I15" s="198"/>
-      <c r="J15" s="199" t="s">
+      <c r="F15" s="191"/>
+      <c r="G15" s="191"/>
+      <c r="H15" s="191"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="192" t="s">
         <v>11</v>
       </c>
       <c r="K15" s="19" t="s">
@@ -3552,11 +3552,11 @@
       <c r="G16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="199" t="s">
+      <c r="H16" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="199"/>
-      <c r="J16" s="199"/>
+      <c r="I16" s="192"/>
+      <c r="J16" s="192"/>
       <c r="K16" s="19"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -3564,15 +3564,15 @@
     <row r="17" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="101"/>
-      <c r="C17" s="200" t="s">
+      <c r="C17" s="193" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="194"/>
+      <c r="H17" s="194"/>
+      <c r="I17" s="195"/>
       <c r="J17" s="55"/>
       <c r="K17" s="56"/>
       <c r="L17" s="5"/>
@@ -3581,13 +3581,13 @@
     <row r="18" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="71"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="204"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="204"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="205"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
       <c r="J18" s="120"/>
       <c r="K18" s="121"/>
       <c r="L18" s="5"/>
@@ -3613,10 +3613,10 @@
       <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="185" t="s">
+      <c r="H19" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="185"/>
+      <c r="I19" s="197"/>
       <c r="J19" s="73"/>
       <c r="K19" s="74"/>
       <c r="L19" s="5"/>
@@ -3625,13 +3625,13 @@
     <row r="20" spans="1:13" ht="73.8" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="79"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="187"/>
-      <c r="E20" s="187"/>
-      <c r="F20" s="188"/>
+      <c r="C20" s="198"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="199"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="80"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="190"/>
+      <c r="H20" s="201"/>
+      <c r="I20" s="202"/>
       <c r="J20" s="75"/>
       <c r="K20" s="75"/>
       <c r="L20" s="5"/>
@@ -3674,10 +3674,10 @@
       <c r="E22" s="138"/>
       <c r="F22" s="141"/>
       <c r="G22" s="142"/>
-      <c r="H22" s="191" t="s">
+      <c r="H22" s="203" t="s">
         <v>72</v>
       </c>
-      <c r="I22" s="192"/>
+      <c r="I22" s="204"/>
       <c r="J22" s="143"/>
       <c r="K22" s="143"/>
       <c r="L22" s="5"/>
@@ -3701,10 +3701,10 @@
       <c r="G23" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="193" t="s">
+      <c r="H23" s="205" t="s">
         <v>38</v>
       </c>
-      <c r="I23" s="193"/>
+      <c r="I23" s="205"/>
       <c r="J23" s="60"/>
       <c r="K23" s="61"/>
       <c r="L23" s="5"/>
@@ -3722,10 +3722,10 @@
       <c r="G24" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="194" t="s">
+      <c r="H24" s="206" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="194"/>
+      <c r="I24" s="206"/>
       <c r="J24" s="64"/>
       <c r="K24" s="64"/>
       <c r="L24" s="5"/>
@@ -3751,10 +3751,10 @@
       <c r="G25" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="179" t="s">
+      <c r="H25" s="207" t="s">
         <v>70</v>
       </c>
-      <c r="I25" s="180"/>
+      <c r="I25" s="208"/>
       <c r="J25" s="65"/>
       <c r="K25" s="65"/>
       <c r="L25" s="5"/>
@@ -3776,10 +3776,10 @@
       <c r="G26" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="181" t="s">
+      <c r="H26" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="182"/>
+      <c r="I26" s="210"/>
       <c r="J26" s="65"/>
       <c r="K26" s="65"/>
       <c r="L26" s="5"/>
@@ -3820,10 +3820,10 @@
       <c r="G28" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="179" t="s">
+      <c r="H28" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="180"/>
+      <c r="I28" s="208"/>
       <c r="J28" s="65"/>
       <c r="K28" s="65"/>
       <c r="L28" s="5"/>
@@ -3845,8 +3845,8 @@
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="68"/>
-      <c r="H29" s="179"/>
-      <c r="I29" s="180"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
       <c r="J29" s="65"/>
       <c r="K29" s="65"/>
       <c r="L29" s="5"/>
@@ -3860,8 +3860,8 @@
       <c r="E30" s="83"/>
       <c r="F30" s="84"/>
       <c r="G30" s="84"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="184"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="212"/>
       <c r="J30" s="84"/>
       <c r="K30" s="84"/>
       <c r="L30" s="5"/>
@@ -3887,10 +3887,10 @@
       <c r="G31" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="176" t="s">
+      <c r="H31" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="I31" s="176"/>
+      <c r="I31" s="196"/>
       <c r="J31" s="81"/>
       <c r="K31" s="81"/>
       <c r="L31" s="5"/>
@@ -3916,10 +3916,10 @@
       <c r="G32" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="176" t="s">
+      <c r="H32" s="196" t="s">
         <v>31</v>
       </c>
-      <c r="I32" s="176"/>
+      <c r="I32" s="196"/>
       <c r="J32" s="81"/>
       <c r="K32" s="81"/>
       <c r="L32" s="5"/>
@@ -3960,10 +3960,10 @@
       <c r="G34" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="176" t="s">
+      <c r="H34" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="176"/>
+      <c r="I34" s="196"/>
       <c r="J34" s="81"/>
       <c r="K34" s="81"/>
       <c r="L34" s="5"/>
@@ -3989,10 +3989,10 @@
       <c r="G35" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="176" t="s">
+      <c r="H35" s="196" t="s">
         <v>31</v>
       </c>
-      <c r="I35" s="176"/>
+      <c r="I35" s="196"/>
       <c r="J35" s="81"/>
       <c r="K35" s="81"/>
       <c r="L35" s="5"/>
@@ -4033,10 +4033,10 @@
       <c r="G37" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="169" t="s">
+      <c r="H37" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="169"/>
+      <c r="I37" s="214"/>
       <c r="J37" s="78"/>
       <c r="K37" s="78"/>
       <c r="L37" s="5"/>
@@ -4058,8 +4058,8 @@
       </c>
       <c r="F38" s="89"/>
       <c r="G38" s="89"/>
-      <c r="H38" s="170"/>
-      <c r="I38" s="170"/>
+      <c r="H38" s="215"/>
+      <c r="I38" s="215"/>
       <c r="J38" s="78"/>
       <c r="K38" s="78"/>
       <c r="L38" s="5"/>
@@ -4073,8 +4073,8 @@
       <c r="E39" s="123"/>
       <c r="F39" s="124"/>
       <c r="G39" s="124"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="178"/>
+      <c r="H39" s="216"/>
+      <c r="I39" s="217"/>
       <c r="J39" s="124"/>
       <c r="K39" s="124"/>
       <c r="L39" s="5"/>
@@ -4100,10 +4100,10 @@
       <c r="G40" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="173" t="s">
+      <c r="H40" s="218" t="s">
         <v>55</v>
       </c>
-      <c r="I40" s="173"/>
+      <c r="I40" s="218"/>
       <c r="J40" s="127"/>
       <c r="K40" s="127"/>
       <c r="L40" s="5"/>
@@ -4127,10 +4127,10 @@
       <c r="G41" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="173" t="s">
+      <c r="H41" s="218" t="s">
         <v>56</v>
       </c>
-      <c r="I41" s="173"/>
+      <c r="I41" s="218"/>
       <c r="J41" s="127"/>
       <c r="K41" s="127"/>
       <c r="L41" s="5"/>
@@ -4154,15 +4154,15 @@
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="137"/>
-      <c r="C43" s="174" t="s">
+      <c r="C43" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="174"/>
-      <c r="E43" s="174"/>
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="167"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219"/>
+      <c r="H43" s="220"/>
+      <c r="I43" s="221"/>
       <c r="J43" s="131"/>
       <c r="K43" s="131"/>
       <c r="L43" s="5"/>
@@ -4184,10 +4184,10 @@
       <c r="G44" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="175" t="s">
+      <c r="H44" s="213" t="s">
         <v>58</v>
       </c>
-      <c r="I44" s="175"/>
+      <c r="I44" s="213"/>
       <c r="J44" s="131"/>
       <c r="K44" s="131"/>
       <c r="L44" s="5"/>
@@ -4207,10 +4207,10 @@
       <c r="G45" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="H45" s="175" t="s">
+      <c r="H45" s="213" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="175"/>
+      <c r="I45" s="213"/>
       <c r="J45" s="131"/>
       <c r="K45" s="131"/>
       <c r="L45" s="5"/>
@@ -4228,8 +4228,8 @@
       <c r="E46" s="130"/>
       <c r="F46" s="131"/>
       <c r="G46" s="131"/>
-      <c r="H46" s="166"/>
-      <c r="I46" s="167"/>
+      <c r="H46" s="220"/>
+      <c r="I46" s="221"/>
       <c r="J46" s="131"/>
       <c r="K46" s="131"/>
       <c r="L46" s="5"/>
@@ -4247,8 +4247,8 @@
       <c r="E47" s="130"/>
       <c r="F47" s="131"/>
       <c r="G47" s="131"/>
-      <c r="H47" s="166"/>
-      <c r="I47" s="167"/>
+      <c r="H47" s="220"/>
+      <c r="I47" s="221"/>
       <c r="J47" s="131"/>
       <c r="K47" s="131"/>
       <c r="L47" s="5"/>
@@ -4262,8 +4262,8 @@
       <c r="E48" s="116"/>
       <c r="F48" s="117"/>
       <c r="G48" s="117"/>
-      <c r="H48" s="168"/>
-      <c r="I48" s="168"/>
+      <c r="H48" s="223"/>
+      <c r="I48" s="223"/>
       <c r="J48" s="117"/>
       <c r="K48" s="117"/>
       <c r="L48" s="5"/>
@@ -4289,10 +4289,10 @@
       <c r="G49" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="169" t="s">
+      <c r="H49" s="214" t="s">
         <v>49</v>
       </c>
-      <c r="I49" s="169"/>
+      <c r="I49" s="214"/>
       <c r="J49" s="78"/>
       <c r="K49" s="78"/>
       <c r="L49" s="5"/>
@@ -4312,8 +4312,8 @@
       <c r="E50" s="89"/>
       <c r="F50" s="89"/>
       <c r="G50" s="89"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="170"/>
+      <c r="H50" s="215"/>
+      <c r="I50" s="215"/>
       <c r="J50" s="78"/>
       <c r="K50" s="78"/>
       <c r="L50" s="5"/>
@@ -4352,10 +4352,10 @@
       <c r="G52" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="H52" s="171" t="s">
+      <c r="H52" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="I52" s="172"/>
+      <c r="I52" s="225"/>
       <c r="J52" s="114"/>
       <c r="K52" s="103"/>
       <c r="L52" s="5"/>
@@ -4375,10 +4375,10 @@
       <c r="G53" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="161" t="s">
+      <c r="H53" s="226" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="161"/>
+      <c r="I53" s="226"/>
       <c r="J53" s="114"/>
       <c r="K53" s="103"/>
       <c r="L53" s="5"/>
@@ -4419,10 +4419,10 @@
       <c r="G55" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="162" t="s">
+      <c r="H55" s="227" t="s">
         <v>50</v>
       </c>
-      <c r="I55" s="162"/>
+      <c r="I55" s="227"/>
       <c r="J55" s="90"/>
       <c r="K55" s="77"/>
       <c r="L55" s="5"/>
@@ -4438,8 +4438,8 @@
       <c r="E56" s="46"/>
       <c r="F56" s="47"/>
       <c r="G56" s="96"/>
-      <c r="H56" s="163"/>
-      <c r="I56" s="163"/>
+      <c r="H56" s="228"/>
+      <c r="I56" s="228"/>
       <c r="J56" s="90"/>
       <c r="K56" s="90"/>
       <c r="L56" s="5"/>
@@ -4453,8 +4453,8 @@
       <c r="E57" s="49"/>
       <c r="F57" s="50"/>
       <c r="G57" s="48"/>
-      <c r="H57" s="164"/>
-      <c r="I57" s="165"/>
+      <c r="H57" s="229"/>
+      <c r="I57" s="230"/>
       <c r="J57" s="51"/>
       <c r="K57" s="51"/>
       <c r="L57" s="5"/>
@@ -4468,8 +4468,8 @@
       <c r="E58" s="16"/>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
-      <c r="H58" s="158"/>
-      <c r="I58" s="158"/>
+      <c r="H58" s="222"/>
+      <c r="I58" s="222"/>
       <c r="J58" s="22"/>
       <c r="K58" s="23"/>
       <c r="L58" s="2"/>
@@ -4483,8 +4483,8 @@
       <c r="E59" s="16"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
+      <c r="H59" s="222"/>
+      <c r="I59" s="222"/>
       <c r="J59" s="22"/>
       <c r="K59" s="23"/>
       <c r="L59" s="2"/>
@@ -4498,8 +4498,8 @@
       <c r="E60" s="16"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
-      <c r="H60" s="152"/>
-      <c r="I60" s="152"/>
+      <c r="H60" s="232"/>
+      <c r="I60" s="232"/>
       <c r="J60" s="22"/>
       <c r="K60" s="23"/>
       <c r="L60" s="2"/>
@@ -4513,8 +4513,8 @@
       <c r="E61" s="18"/>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
-      <c r="H61" s="155"/>
-      <c r="I61" s="156"/>
+      <c r="H61" s="233"/>
+      <c r="I61" s="234"/>
       <c r="J61" s="22"/>
       <c r="K61" s="23"/>
       <c r="L61" s="2"/>
@@ -4530,8 +4530,8 @@
       <c r="E62" s="18"/>
       <c r="F62" s="22"/>
       <c r="G62" s="22"/>
-      <c r="H62" s="157"/>
-      <c r="I62" s="157"/>
+      <c r="H62" s="235"/>
+      <c r="I62" s="235"/>
       <c r="J62" s="19"/>
       <c r="K62" s="21"/>
       <c r="L62" s="2"/>
@@ -4545,8 +4545,8 @@
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
       <c r="G63" s="19"/>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158"/>
+      <c r="H63" s="222"/>
+      <c r="I63" s="222"/>
       <c r="J63" s="19"/>
       <c r="K63" s="21"/>
       <c r="L63" s="2"/>
@@ -4560,8 +4560,8 @@
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
-      <c r="H64" s="159"/>
-      <c r="I64" s="160"/>
+      <c r="H64" s="236"/>
+      <c r="I64" s="237"/>
       <c r="J64" s="19"/>
       <c r="K64" s="21"/>
       <c r="L64" s="2"/>
@@ -4575,8 +4575,8 @@
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
-      <c r="H65" s="158"/>
-      <c r="I65" s="158"/>
+      <c r="H65" s="222"/>
+      <c r="I65" s="222"/>
       <c r="J65" s="20"/>
       <c r="K65" s="21"/>
       <c r="L65" s="2"/>
@@ -4590,8 +4590,8 @@
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
       <c r="G66" s="19"/>
-      <c r="H66" s="152"/>
-      <c r="I66" s="152"/>
+      <c r="H66" s="232"/>
+      <c r="I66" s="232"/>
       <c r="J66" s="20"/>
       <c r="K66" s="21"/>
       <c r="L66" s="2"/>
@@ -4605,8 +4605,8 @@
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
-      <c r="H67" s="153"/>
-      <c r="I67" s="153"/>
+      <c r="H67" s="238"/>
+      <c r="I67" s="238"/>
       <c r="J67" s="29"/>
       <c r="K67" s="14"/>
       <c r="L67" s="2"/>
@@ -4620,8 +4620,8 @@
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
-      <c r="H68" s="153"/>
-      <c r="I68" s="153"/>
+      <c r="H68" s="238"/>
+      <c r="I68" s="238"/>
       <c r="J68" s="29"/>
       <c r="K68" s="14"/>
       <c r="L68" s="2"/>
@@ -4635,8 +4635,8 @@
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
-      <c r="H69" s="153"/>
-      <c r="I69" s="153"/>
+      <c r="H69" s="238"/>
+      <c r="I69" s="238"/>
       <c r="J69" s="29"/>
       <c r="K69" s="14"/>
       <c r="L69" s="2"/>
@@ -4650,8 +4650,8 @@
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
       <c r="G70" s="12"/>
-      <c r="H70" s="153"/>
-      <c r="I70" s="153"/>
+      <c r="H70" s="238"/>
+      <c r="I70" s="238"/>
       <c r="J70" s="29"/>
       <c r="K70" s="14"/>
       <c r="L70" s="2"/>
@@ -4665,8 +4665,8 @@
       <c r="E71" s="32"/>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="154"/>
+      <c r="H71" s="231"/>
+      <c r="I71" s="231"/>
       <c r="J71" s="33"/>
       <c r="K71" s="34"/>
       <c r="L71" s="2"/>
@@ -4809,6 +4809,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G13"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H64:I64"/>
     <mergeCell ref="C43:G43"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="H16:I16"/>
@@ -4825,79 +4898,6 @@
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G13"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H49:I49"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -5707,21 +5707,21 @@
       <c r="B2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="225">
+      <c r="C2" s="152">
         <v>46296</v>
       </c>
-      <c r="D2" s="226"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="228" t="s">
+      <c r="D2" s="153"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230" t="s">
+      <c r="G2" s="156"/>
+      <c r="H2" s="157" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="230"/>
-      <c r="J2" s="230"/>
-      <c r="K2" s="231"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="158"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
@@ -5730,19 +5730,19 @@
       <c r="B3" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="226"/>
-      <c r="E3" s="227"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="233"/>
-      <c r="H3" s="236" t="s">
+      <c r="D3" s="153"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="209"/>
-      <c r="K3" s="210"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="166"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
@@ -5751,17 +5751,17 @@
       <c r="B4" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="222" t="s">
+      <c r="C4" s="167" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="223"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="235"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="210"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="166"/>
+      <c r="J4" s="170"/>
+      <c r="K4" s="166"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
@@ -5770,17 +5770,17 @@
       <c r="B5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="222">
+      <c r="C5" s="167">
         <v>5160507</v>
       </c>
-      <c r="D5" s="223"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="234"/>
-      <c r="G5" s="235"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="210"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="162"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="166"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="166"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
@@ -5789,17 +5789,17 @@
       <c r="B6" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="222" t="s">
+      <c r="C6" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="223"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="234"/>
-      <c r="G6" s="235"/>
-      <c r="H6" s="209"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="209"/>
-      <c r="K6" s="210"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="162"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="166"/>
+      <c r="J6" s="165"/>
+      <c r="K6" s="166"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
@@ -5808,17 +5808,17 @@
       <c r="B7" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="167" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="223"/>
-      <c r="E7" s="224"/>
-      <c r="F7" s="234"/>
-      <c r="G7" s="235"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="209"/>
-      <c r="K7" s="210"/>
+      <c r="D7" s="168"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="166"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="166"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
@@ -5827,17 +5827,17 @@
       <c r="B8" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="225" t="s">
+      <c r="C8" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="226"/>
-      <c r="E8" s="227"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="235"/>
-      <c r="H8" s="209"/>
-      <c r="I8" s="210"/>
-      <c r="J8" s="209"/>
-      <c r="K8" s="210"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="161"/>
+      <c r="G8" s="162"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="165"/>
+      <c r="K8" s="166"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
@@ -5846,15 +5846,15 @@
       <c r="B9" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="216"/>
-      <c r="D9" s="217"/>
-      <c r="E9" s="218"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
-      <c r="J9" s="209"/>
-      <c r="K9" s="210"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
+      <c r="F9" s="161"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="166"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
@@ -5863,15 +5863,15 @@
       <c r="B10" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="219"/>
-      <c r="D10" s="220"/>
-      <c r="E10" s="221"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="209"/>
-      <c r="I10" s="210"/>
-      <c r="J10" s="209"/>
-      <c r="K10" s="210"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="180"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="161"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="165"/>
+      <c r="K10" s="166"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
@@ -5880,13 +5880,13 @@
       <c r="B11" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="206"/>
-      <c r="D11" s="207"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="234"/>
-      <c r="G11" s="235"/>
-      <c r="H11" s="209"/>
-      <c r="I11" s="210"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="166"/>
       <c r="J11" s="53"/>
       <c r="K11" s="54"/>
       <c r="L11" s="2"/>
@@ -5897,15 +5897,15 @@
       <c r="B12" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="211"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="234"/>
-      <c r="G12" s="235"/>
-      <c r="H12" s="209"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="214"/>
-      <c r="K12" s="215"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="172"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
@@ -5914,13 +5914,13 @@
       <c r="B13" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="206"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="234"/>
-      <c r="G13" s="235"/>
-      <c r="H13" s="209"/>
-      <c r="I13" s="210"/>
+      <c r="C13" s="173"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="161"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="166"/>
       <c r="J13" s="35"/>
       <c r="K13" s="17"/>
       <c r="L13" s="2"/>
@@ -5931,17 +5931,17 @@
       <c r="B14" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="195" t="s">
+      <c r="C14" s="188" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="196"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="198" t="s">
+      <c r="D14" s="189"/>
+      <c r="E14" s="190"/>
+      <c r="F14" s="191" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="198"/>
-      <c r="H14" s="198"/>
-      <c r="I14" s="198"/>
+      <c r="G14" s="191"/>
+      <c r="H14" s="191"/>
+      <c r="I14" s="191"/>
       <c r="J14" s="36"/>
       <c r="K14" s="19"/>
       <c r="L14" s="2"/>
@@ -5959,11 +5959,11 @@
       <c r="E15" s="38">
         <v>1</v>
       </c>
-      <c r="F15" s="198"/>
-      <c r="G15" s="198"/>
-      <c r="H15" s="198"/>
-      <c r="I15" s="198"/>
-      <c r="J15" s="199" t="s">
+      <c r="F15" s="191"/>
+      <c r="G15" s="191"/>
+      <c r="H15" s="191"/>
+      <c r="I15" s="191"/>
+      <c r="J15" s="192" t="s">
         <v>11</v>
       </c>
       <c r="K15" s="19" t="s">
@@ -5992,11 +5992,11 @@
       <c r="G16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="199" t="s">
+      <c r="H16" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="199"/>
-      <c r="J16" s="199"/>
+      <c r="I16" s="192"/>
+      <c r="J16" s="192"/>
       <c r="K16" s="19"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -6004,15 +6004,15 @@
     <row r="17" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="101"/>
-      <c r="C17" s="200" t="s">
+      <c r="C17" s="193" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
-      <c r="F17" s="201"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="202"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="194"/>
+      <c r="G17" s="194"/>
+      <c r="H17" s="194"/>
+      <c r="I17" s="195"/>
       <c r="J17" s="55"/>
       <c r="K17" s="56"/>
       <c r="L17" s="5"/>
@@ -6021,13 +6021,13 @@
     <row r="18" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="71"/>
-      <c r="C18" s="203"/>
-      <c r="D18" s="204"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="204"/>
-      <c r="H18" s="204"/>
-      <c r="I18" s="205"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="184"/>
       <c r="J18" s="120"/>
       <c r="K18" s="121"/>
       <c r="L18" s="5"/>
@@ -6053,10 +6053,10 @@
       <c r="G19" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="185" t="s">
+      <c r="H19" s="197" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="185"/>
+      <c r="I19" s="197"/>
       <c r="J19" s="73"/>
       <c r="K19" s="74"/>
       <c r="L19" s="5"/>
@@ -6065,13 +6065,13 @@
     <row r="20" spans="1:13" ht="73.8" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="79"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="187"/>
-      <c r="E20" s="187"/>
-      <c r="F20" s="188"/>
+      <c r="C20" s="198"/>
+      <c r="D20" s="199"/>
+      <c r="E20" s="199"/>
+      <c r="F20" s="200"/>
       <c r="G20" s="80"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="190"/>
+      <c r="H20" s="201"/>
+      <c r="I20" s="202"/>
       <c r="J20" s="75"/>
       <c r="K20" s="75"/>
       <c r="L20" s="5"/>
@@ -6114,10 +6114,10 @@
       <c r="E22" s="138"/>
       <c r="F22" s="141"/>
       <c r="G22" s="142"/>
-      <c r="H22" s="191" t="s">
+      <c r="H22" s="203" t="s">
         <v>72</v>
       </c>
-      <c r="I22" s="192"/>
+      <c r="I22" s="204"/>
       <c r="J22" s="143"/>
       <c r="K22" s="143"/>
       <c r="L22" s="5"/>
@@ -6141,10 +6141,10 @@
       <c r="G23" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="193" t="s">
+      <c r="H23" s="205" t="s">
         <v>38</v>
       </c>
-      <c r="I23" s="193"/>
+      <c r="I23" s="205"/>
       <c r="J23" s="60"/>
       <c r="K23" s="61"/>
       <c r="L23" s="5"/>
@@ -6162,10 +6162,10 @@
       <c r="G24" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="194" t="s">
+      <c r="H24" s="206" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="194"/>
+      <c r="I24" s="206"/>
       <c r="J24" s="64"/>
       <c r="K24" s="64"/>
       <c r="L24" s="5"/>
@@ -6191,10 +6191,10 @@
       <c r="G25" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="179" t="s">
+      <c r="H25" s="207" t="s">
         <v>70</v>
       </c>
-      <c r="I25" s="180"/>
+      <c r="I25" s="208"/>
       <c r="J25" s="65"/>
       <c r="K25" s="65"/>
       <c r="L25" s="5"/>
@@ -6216,10 +6216,10 @@
       <c r="G26" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="181" t="s">
+      <c r="H26" s="209" t="s">
         <v>71</v>
       </c>
-      <c r="I26" s="182"/>
+      <c r="I26" s="210"/>
       <c r="J26" s="65"/>
       <c r="K26" s="65"/>
       <c r="L26" s="5"/>
@@ -6260,10 +6260,10 @@
       <c r="G28" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="179" t="s">
+      <c r="H28" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="180"/>
+      <c r="I28" s="208"/>
       <c r="J28" s="65"/>
       <c r="K28" s="65"/>
       <c r="L28" s="5"/>
@@ -6285,8 +6285,8 @@
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="68"/>
-      <c r="H29" s="179"/>
-      <c r="I29" s="180"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="208"/>
       <c r="J29" s="65"/>
       <c r="K29" s="65"/>
       <c r="L29" s="5"/>
@@ -6300,8 +6300,8 @@
       <c r="E30" s="83"/>
       <c r="F30" s="84"/>
       <c r="G30" s="84"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="184"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="212"/>
       <c r="J30" s="84"/>
       <c r="K30" s="84"/>
       <c r="L30" s="5"/>
@@ -6327,10 +6327,10 @@
       <c r="G31" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="H31" s="176" t="s">
+      <c r="H31" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="I31" s="176"/>
+      <c r="I31" s="196"/>
       <c r="J31" s="81"/>
       <c r="K31" s="81"/>
       <c r="L31" s="5"/>
@@ -6356,10 +6356,10 @@
       <c r="G32" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="H32" s="176" t="s">
+      <c r="H32" s="196" t="s">
         <v>31</v>
       </c>
-      <c r="I32" s="176"/>
+      <c r="I32" s="196"/>
       <c r="J32" s="81"/>
       <c r="K32" s="81"/>
       <c r="L32" s="5"/>
@@ -6400,10 +6400,10 @@
       <c r="G34" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="H34" s="176" t="s">
+      <c r="H34" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="176"/>
+      <c r="I34" s="196"/>
       <c r="J34" s="81"/>
       <c r="K34" s="81"/>
       <c r="L34" s="5"/>
@@ -6429,10 +6429,10 @@
       <c r="G35" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="176" t="s">
+      <c r="H35" s="196" t="s">
         <v>31</v>
       </c>
-      <c r="I35" s="176"/>
+      <c r="I35" s="196"/>
       <c r="J35" s="81"/>
       <c r="K35" s="81"/>
       <c r="L35" s="5"/>
@@ -6473,10 +6473,10 @@
       <c r="G37" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="169" t="s">
+      <c r="H37" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="169"/>
+      <c r="I37" s="214"/>
       <c r="J37" s="78"/>
       <c r="K37" s="78"/>
       <c r="L37" s="5"/>
@@ -6498,8 +6498,8 @@
       </c>
       <c r="F38" s="89"/>
       <c r="G38" s="89"/>
-      <c r="H38" s="170"/>
-      <c r="I38" s="170"/>
+      <c r="H38" s="215"/>
+      <c r="I38" s="215"/>
       <c r="J38" s="78"/>
       <c r="K38" s="78"/>
       <c r="L38" s="5"/>
@@ -6513,8 +6513,8 @@
       <c r="E39" s="123"/>
       <c r="F39" s="124"/>
       <c r="G39" s="124"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="178"/>
+      <c r="H39" s="216"/>
+      <c r="I39" s="217"/>
       <c r="J39" s="124"/>
       <c r="K39" s="124"/>
       <c r="L39" s="5"/>
@@ -6540,10 +6540,10 @@
       <c r="G40" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="H40" s="173" t="s">
+      <c r="H40" s="218" t="s">
         <v>55</v>
       </c>
-      <c r="I40" s="173"/>
+      <c r="I40" s="218"/>
       <c r="J40" s="127"/>
       <c r="K40" s="127"/>
       <c r="L40" s="5"/>
@@ -6567,10 +6567,10 @@
       <c r="G41" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="173" t="s">
+      <c r="H41" s="218" t="s">
         <v>56</v>
       </c>
-      <c r="I41" s="173"/>
+      <c r="I41" s="218"/>
       <c r="J41" s="127"/>
       <c r="K41" s="127"/>
       <c r="L41" s="5"/>
@@ -6594,15 +6594,15 @@
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="6"/>
       <c r="B43" s="137"/>
-      <c r="C43" s="174" t="s">
+      <c r="C43" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="D43" s="174"/>
-      <c r="E43" s="174"/>
-      <c r="F43" s="174"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="166"/>
-      <c r="I43" s="167"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219"/>
+      <c r="H43" s="220"/>
+      <c r="I43" s="221"/>
       <c r="J43" s="131"/>
       <c r="K43" s="131"/>
       <c r="L43" s="5"/>
@@ -6624,10 +6624,10 @@
       <c r="G44" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="H44" s="175" t="s">
+      <c r="H44" s="213" t="s">
         <v>58</v>
       </c>
-      <c r="I44" s="175"/>
+      <c r="I44" s="213"/>
       <c r="J44" s="131"/>
       <c r="K44" s="131"/>
       <c r="L44" s="5"/>
@@ -6647,10 +6647,10 @@
       <c r="G45" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="H45" s="175" t="s">
+      <c r="H45" s="213" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="175"/>
+      <c r="I45" s="213"/>
       <c r="J45" s="131"/>
       <c r="K45" s="131"/>
       <c r="L45" s="5"/>
@@ -6668,8 +6668,8 @@
       <c r="E46" s="130"/>
       <c r="F46" s="131"/>
       <c r="G46" s="131"/>
-      <c r="H46" s="166"/>
-      <c r="I46" s="167"/>
+      <c r="H46" s="220"/>
+      <c r="I46" s="221"/>
       <c r="J46" s="131"/>
       <c r="K46" s="131"/>
       <c r="L46" s="5"/>
@@ -6687,8 +6687,8 @@
       <c r="E47" s="130"/>
       <c r="F47" s="131"/>
       <c r="G47" s="131"/>
-      <c r="H47" s="166"/>
-      <c r="I47" s="167"/>
+      <c r="H47" s="220"/>
+      <c r="I47" s="221"/>
       <c r="J47" s="131"/>
       <c r="K47" s="131"/>
       <c r="L47" s="5"/>
@@ -6702,8 +6702,8 @@
       <c r="E48" s="116"/>
       <c r="F48" s="117"/>
       <c r="G48" s="117"/>
-      <c r="H48" s="168"/>
-      <c r="I48" s="168"/>
+      <c r="H48" s="223"/>
+      <c r="I48" s="223"/>
       <c r="J48" s="117"/>
       <c r="K48" s="117"/>
       <c r="L48" s="5"/>
@@ -6729,10 +6729,10 @@
       <c r="G49" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="169" t="s">
+      <c r="H49" s="214" t="s">
         <v>49</v>
       </c>
-      <c r="I49" s="169"/>
+      <c r="I49" s="214"/>
       <c r="J49" s="78"/>
       <c r="K49" s="78"/>
       <c r="L49" s="5"/>
@@ -6752,8 +6752,8 @@
       <c r="E50" s="89"/>
       <c r="F50" s="89"/>
       <c r="G50" s="89"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="170"/>
+      <c r="H50" s="215"/>
+      <c r="I50" s="215"/>
       <c r="J50" s="78"/>
       <c r="K50" s="78"/>
       <c r="L50" s="5"/>
@@ -6792,10 +6792,10 @@
       <c r="G52" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="H52" s="171" t="s">
+      <c r="H52" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="I52" s="172"/>
+      <c r="I52" s="225"/>
       <c r="J52" s="114"/>
       <c r="K52" s="103"/>
       <c r="L52" s="5"/>
@@ -6815,10 +6815,10 @@
       <c r="G53" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="161" t="s">
+      <c r="H53" s="226" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="161"/>
+      <c r="I53" s="226"/>
       <c r="J53" s="114"/>
       <c r="K53" s="103"/>
       <c r="L53" s="5"/>
@@ -6859,10 +6859,10 @@
       <c r="G55" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="162" t="s">
+      <c r="H55" s="227" t="s">
         <v>50</v>
       </c>
-      <c r="I55" s="162"/>
+      <c r="I55" s="227"/>
       <c r="J55" s="90"/>
       <c r="K55" s="77"/>
       <c r="L55" s="5"/>
@@ -6878,8 +6878,8 @@
       <c r="E56" s="46"/>
       <c r="F56" s="47"/>
       <c r="G56" s="96"/>
-      <c r="H56" s="163"/>
-      <c r="I56" s="163"/>
+      <c r="H56" s="228"/>
+      <c r="I56" s="228"/>
       <c r="J56" s="90"/>
       <c r="K56" s="90"/>
       <c r="L56" s="5"/>
@@ -6895,8 +6895,8 @@
       <c r="E57" s="49"/>
       <c r="F57" s="50"/>
       <c r="G57" s="48"/>
-      <c r="H57" s="164"/>
-      <c r="I57" s="165"/>
+      <c r="H57" s="229"/>
+      <c r="I57" s="230"/>
       <c r="J57" s="51"/>
       <c r="K57" s="51"/>
       <c r="L57" s="5"/>
@@ -6910,8 +6910,8 @@
       <c r="E58" s="16"/>
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
-      <c r="H58" s="158"/>
-      <c r="I58" s="158"/>
+      <c r="H58" s="222"/>
+      <c r="I58" s="222"/>
       <c r="J58" s="22"/>
       <c r="K58" s="23"/>
       <c r="L58" s="2"/>
@@ -6925,8 +6925,8 @@
       <c r="E59" s="16"/>
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
+      <c r="H59" s="222"/>
+      <c r="I59" s="222"/>
       <c r="J59" s="22"/>
       <c r="K59" s="23"/>
       <c r="L59" s="2"/>
@@ -6940,8 +6940,8 @@
       <c r="E60" s="16"/>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
-      <c r="H60" s="152"/>
-      <c r="I60" s="152"/>
+      <c r="H60" s="232"/>
+      <c r="I60" s="232"/>
       <c r="J60" s="22"/>
       <c r="K60" s="23"/>
       <c r="L60" s="2"/>
@@ -6955,8 +6955,8 @@
       <c r="E61" s="18"/>
       <c r="F61" s="22"/>
       <c r="G61" s="22"/>
-      <c r="H61" s="155"/>
-      <c r="I61" s="156"/>
+      <c r="H61" s="233"/>
+      <c r="I61" s="234"/>
       <c r="J61" s="22"/>
       <c r="K61" s="23"/>
       <c r="L61" s="2"/>
@@ -6972,8 +6972,8 @@
       <c r="E62" s="18"/>
       <c r="F62" s="22"/>
       <c r="G62" s="22"/>
-      <c r="H62" s="157"/>
-      <c r="I62" s="157"/>
+      <c r="H62" s="235"/>
+      <c r="I62" s="235"/>
       <c r="J62" s="19"/>
       <c r="K62" s="21"/>
       <c r="L62" s="2"/>
@@ -6987,8 +6987,8 @@
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
       <c r="G63" s="19"/>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158"/>
+      <c r="H63" s="222"/>
+      <c r="I63" s="222"/>
       <c r="J63" s="19"/>
       <c r="K63" s="21"/>
       <c r="L63" s="2"/>
@@ -7002,8 +7002,8 @@
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
       <c r="G64" s="19"/>
-      <c r="H64" s="159"/>
-      <c r="I64" s="160"/>
+      <c r="H64" s="236"/>
+      <c r="I64" s="237"/>
       <c r="J64" s="19"/>
       <c r="K64" s="21"/>
       <c r="L64" s="2"/>
@@ -7017,8 +7017,8 @@
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19"/>
-      <c r="H65" s="158"/>
-      <c r="I65" s="158"/>
+      <c r="H65" s="222"/>
+      <c r="I65" s="222"/>
       <c r="J65" s="20"/>
       <c r="K65" s="21"/>
       <c r="L65" s="2"/>
@@ -7032,8 +7032,8 @@
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
       <c r="G66" s="19"/>
-      <c r="H66" s="152"/>
-      <c r="I66" s="152"/>
+      <c r="H66" s="232"/>
+      <c r="I66" s="232"/>
       <c r="J66" s="20"/>
       <c r="K66" s="21"/>
       <c r="L66" s="2"/>
@@ -7047,8 +7047,8 @@
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
-      <c r="H67" s="153"/>
-      <c r="I67" s="153"/>
+      <c r="H67" s="238"/>
+      <c r="I67" s="238"/>
       <c r="J67" s="29"/>
       <c r="K67" s="14"/>
       <c r="L67" s="2"/>
@@ -7062,8 +7062,8 @@
       <c r="E68" s="12"/>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
-      <c r="H68" s="153"/>
-      <c r="I68" s="153"/>
+      <c r="H68" s="238"/>
+      <c r="I68" s="238"/>
       <c r="J68" s="29"/>
       <c r="K68" s="14"/>
       <c r="L68" s="2"/>
@@ -7077,8 +7077,8 @@
       <c r="E69" s="12"/>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
-      <c r="H69" s="153"/>
-      <c r="I69" s="153"/>
+      <c r="H69" s="238"/>
+      <c r="I69" s="238"/>
       <c r="J69" s="29"/>
       <c r="K69" s="14"/>
       <c r="L69" s="2"/>
@@ -7092,8 +7092,8 @@
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
       <c r="G70" s="12"/>
-      <c r="H70" s="153"/>
-      <c r="I70" s="153"/>
+      <c r="H70" s="238"/>
+      <c r="I70" s="238"/>
       <c r="J70" s="29"/>
       <c r="K70" s="14"/>
       <c r="L70" s="2"/>
@@ -7107,8 +7107,8 @@
       <c r="E71" s="32"/>
       <c r="F71" s="32"/>
       <c r="G71" s="32"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="154"/>
+      <c r="H71" s="231"/>
+      <c r="I71" s="231"/>
       <c r="J71" s="33"/>
       <c r="K71" s="34"/>
       <c r="L71" s="2"/>
@@ -7251,6 +7251,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:I15"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -7267,79 +7340,6 @@
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
